--- a/04_DESIGN_TABLES/DesignTable_1404.xlsx
+++ b/04_DESIGN_TABLES/DesignTable_1404.xlsx
@@ -513,7 +513,7 @@
         <v>1.15</v>
       </c>
       <c r="D3" t="n">
-        <v>0.5</v>
+        <v>0.5620000000000001</v>
       </c>
       <c r="E3" t="n">
         <v>0.5600000000000001</v>
@@ -522,7 +522,7 @@
         <v>0.19</v>
       </c>
       <c r="G3" t="n">
-        <v>0.11</v>
+        <v>0.13</v>
       </c>
       <c r="H3" t="n">
         <v>0.405</v>
@@ -547,7 +547,12 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>Air-Way s55 only (double-pass 27 rows); D@BORE: OMi WebsitePartsInfo2026.xlsx Items!X88 Side 2 ID = 0.110 (table had 0.13) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]</t>
+          <t>Air-Way s55 only (double-pass 27 rows); D@BORE: OMi WebsitePartsInfo2026.xlsx Items!X88 Side 2 ID = 0.110 (table had 0.13) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; C1HEX@HEX: OMi WebsitePartsInfo2026.xlsx Items!R88 = 0.562 (table had 0.5) [user 2026-10-18 A19]</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>A20 (user 2026-10-18): W@HEX 1.15 -&gt; OMi 1.08 (Items!L88; nut face at OMi's overall length) | A21 (user 2026-10-18): D@BORE 0.11 (OMi, batch 14) -&gt; Air-Way 0.13 (0.13 (07_RAW_EXTRACTS\1404.csv col 9 (D))) | A19 (user 2026-10-18, group 3 open): C1HEX@HEX 0.5 -&gt; OMi 0.562 (Items!R88, M051) | A20 HELD (2026-10-18): OMi overall length 1.08 as nut face breaks the measured NPSM swivel (W-L out of range; OMi gives no stem-tip length to pair) -&gt; kept at Air-Way W 1.15; user 2026-10-18: keep Air-Way W, reported to OMi (10_DRAWINGS/for_OMi_LATER)</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -571,10 +576,10 @@
         <v>1.06</v>
       </c>
       <c r="C4" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="D4" t="n">
-        <v>0.63</v>
+        <v>0.6879999999999999</v>
       </c>
       <c r="E4" t="n">
         <v>0.6899999999999999</v>
@@ -583,7 +588,7 @@
         <v>0.19</v>
       </c>
       <c r="G4" t="n">
-        <v>0.21</v>
+        <v>0.19</v>
       </c>
       <c r="H4" t="n">
         <v>0.405</v>
@@ -608,7 +613,12 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>Air-Way s55 only (double-pass 27 rows); D@BORE: OMi WebsitePartsInfo2026.xlsx Items!X89 Side 2 ID = 0.21 (table had 0.19) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]</t>
+          <t>Air-Way s55 only (double-pass 27 rows); D@BORE: OMi WebsitePartsInfo2026.xlsx Items!X89 Side 2 ID = 0.21 (table had 0.19) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; C1HEX@HEX: OMi WebsitePartsInfo2026.xlsx Items!R89 = 0.688 (table had 0.63) [user 2026-10-18 A19]</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>A20 (user 2026-10-18): W@HEX 1.25 -&gt; OMi 1.24 (Items!L89; nut face at OMi's overall length) | A21 (user 2026-10-18): D@BORE 0.21 (OMi, batch 14) -&gt; Air-Way 0.19 (0.19 (07_RAW_EXTRACTS\1404.csv col 9 (D))) | A19 (user 2026-10-18, group 3 open): C1HEX@HEX 0.63 -&gt; OMi 0.688 (Items!R89, M051)</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -693,10 +703,10 @@
         <v>1.19</v>
       </c>
       <c r="C6" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="D6" t="n">
-        <v>0.63</v>
+        <v>0.6879999999999999</v>
       </c>
       <c r="E6" t="n">
         <v>0.5600000000000001</v>
@@ -730,7 +740,12 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>Air-Way s55 only (double-pass 27 rows)</t>
+          <t>Air-Way s55 only (double-pass 27 rows); C1HEX@HEX: OMi WebsitePartsInfo2026.xlsx Items!R90 = 0.688 (table had 0.63) [user 2026-10-18 A19]</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>A20 (user 2026-10-18): W@HEX 1.34 -&gt; OMi 1.33 (Items!L90; nut face at OMi's overall length) | A19 (user 2026-10-18, group 3 open): C1HEX@HEX 0.63 -&gt; OMi 0.688 (Items!R90, M051)</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -757,7 +772,7 @@
         <v>1.44</v>
       </c>
       <c r="D7" t="n">
-        <v>0.63</v>
+        <v>0.6879999999999999</v>
       </c>
       <c r="E7" t="n">
         <v>0.6899999999999999</v>
@@ -766,7 +781,7 @@
         <v>0.28</v>
       </c>
       <c r="G7" t="n">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="H7" t="n">
         <v>0.54</v>
@@ -791,7 +806,12 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>Air-Way s55 only (double-pass 27 rows); D@BORE: OMi WebsitePartsInfo2026.xlsx Items!X91 Side 2 ID = 0.21 (table had 0.22) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]</t>
+          <t>Air-Way s55 only (double-pass 27 rows); D@BORE: OMi WebsitePartsInfo2026.xlsx Items!X91 Side 2 ID = 0.21 (table had 0.22) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; C1HEX@HEX: OMi WebsitePartsInfo2026.xlsx Items!R91 = 0.688 (table had 0.63) [user 2026-10-18 A19]</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>A20 (user 2026-10-18): W@HEX 1.44 -&gt; OMi 1.42 (Items!L91; nut face at OMi's overall length) | A21 (user 2026-10-18): D@BORE 0.21 (OMi, batch 14) -&gt; Air-Way 0.22 (0.22 (07_RAW_EXTRACTS\1404.csv col 9 (D))) | A19 (user 2026-10-18, group 3 open): C1HEX@HEX 0.63 -&gt; OMi 0.688 (Items!R91, M051) | A20 HELD (2026-10-18): OMi overall length 1.42 as nut face breaks the measured NPSM swivel (W-L out of range; OMi gives no stem-tip length to pair) -&gt; kept at Air-Way W 1.44; user 2026-10-18: keep Air-Way W, reported to OMi (10_DRAWINGS/for_OMi_LATER)</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -815,7 +835,7 @@
         <v>1.31</v>
       </c>
       <c r="C8" t="n">
-        <v>1.56</v>
+        <v>1.52</v>
       </c>
       <c r="D8" t="n">
         <v>0.8100000000000001</v>
@@ -855,6 +875,11 @@
           <t>Air-Way s55 only (double-pass 27 rows)</t>
         </is>
       </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>A20 (user 2026-10-18): W@HEX 1.56 -&gt; OMi 1.52 (Items!L92; nut face at OMi's overall length)</t>
+        </is>
+      </c>
       <c r="O8" t="inlineStr">
         <is>
           <t>BUILD</t>
@@ -876,10 +901,10 @@
         <v>1.42</v>
       </c>
       <c r="C9" t="n">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="D9" t="n">
-        <v>0.9399999999999999</v>
+        <v>1</v>
       </c>
       <c r="E9" t="n">
         <v>1</v>
@@ -888,7 +913,7 @@
         <v>0.28</v>
       </c>
       <c r="G9" t="n">
-        <v>0.44</v>
+        <v>0.28</v>
       </c>
       <c r="H9" t="n">
         <v>0.54</v>
@@ -913,7 +938,12 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>Air-Way s55 only (double-pass 27 rows); D@BORE: OMi WebsitePartsInfo2026.xlsx Items!X93 Side 2 ID = 0.44 (table had 0.28) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]</t>
+          <t>Air-Way s55 only (double-pass 27 rows); D@BORE: OMi WebsitePartsInfo2026.xlsx Items!X93 Side 2 ID = 0.44 (table had 0.28) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; C1HEX@HEX: OMi WebsitePartsInfo2026.xlsx Items!R93 = 1.000 (table had 0.94) [user 2026-10-18 A19]</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>A20 (user 2026-10-18): W@HEX 1.75 -&gt; OMi 1.70 (Items!L93; nut face at OMi's overall length) | A21 (user 2026-10-18): D@BORE 0.44 (OMi, batch 14) -&gt; Air-Way 0.28 (0.28 (07_RAW_EXTRACTS\1404.csv col 9 (D))) | A19 (user 2026-10-18, group 3 open): C1HEX@HEX 0.94 -&gt; OMi 1.000 (Items!R93, M051)</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -937,7 +967,7 @@
         <v>1.31</v>
       </c>
       <c r="C10" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="D10" t="n">
         <v>0.75</v>
@@ -949,7 +979,7 @@
         <v>0.41</v>
       </c>
       <c r="G10" t="n">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="H10" t="n">
         <v>0.675</v>
@@ -977,6 +1007,11 @@
           <t>Air-Way s55 only (double-pass 27 rows); D@BORE: OMi WebsitePartsInfo2026.xlsx Items!X94 Side 2 ID = 0.21 (table had 0.22) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]</t>
         </is>
       </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>A20 (user 2026-10-18): W@HEX 1.5 -&gt; OMi 1.49 (Items!L94; nut face at OMi's overall length) | A21 (user 2026-10-18): D@BORE 0.21 (OMi, batch 14) -&gt; Air-Way 0.22 (0.22 (07_RAW_EXTRACTS\1404.csv col 9 (D)))</t>
+        </is>
+      </c>
       <c r="O10" t="inlineStr">
         <is>
           <t>BUILD</t>
@@ -998,10 +1033,10 @@
         <v>1.31</v>
       </c>
       <c r="C11" t="n">
-        <v>1.56</v>
+        <v>1.52</v>
       </c>
       <c r="D11" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.875</v>
       </c>
       <c r="E11" t="n">
         <v>0.88</v>
@@ -1010,7 +1045,7 @@
         <v>0.41</v>
       </c>
       <c r="G11" t="n">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="H11" t="n">
         <v>0.675</v>
@@ -1035,7 +1070,12 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>Air-Way s55 only (double-pass 27 rows); D@BORE: OMi WebsitePartsInfo2026.xlsx Items!X95 Side 2 ID = 0.32 (table had 0.33) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]</t>
+          <t>Air-Way s55 only (double-pass 27 rows); D@BORE: OMi WebsitePartsInfo2026.xlsx Items!X95 Side 2 ID = 0.32 (table had 0.33) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; C1HEX@HEX: OMi WebsitePartsInfo2026.xlsx Items!R95 = 0.875 (table had 0.81) [user 2026-10-18 A19]</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>A20 (user 2026-10-18): W@HEX 1.56 -&gt; OMi 1.52 (Items!L95; nut face at OMi's overall length) | A21 (user 2026-10-18): D@BORE 0.32 (OMi, batch 14) -&gt; Air-Way 0.33 (0.33 (07_RAW_EXTRACTS\1404.csv col 9 (D))) | A19 (user 2026-10-18, group 3 open): C1HEX@HEX 0.81 -&gt; OMi 0.875 (Items!R95, M051)</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -1059,10 +1099,10 @@
         <v>1.42</v>
       </c>
       <c r="C12" t="n">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="D12" t="n">
-        <v>0.9399999999999999</v>
+        <v>1</v>
       </c>
       <c r="E12" t="n">
         <v>1</v>
@@ -1071,7 +1111,7 @@
         <v>0.41</v>
       </c>
       <c r="G12" t="n">
-        <v>0.44</v>
+        <v>0.41</v>
       </c>
       <c r="H12" t="n">
         <v>0.675</v>
@@ -1096,7 +1136,12 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>Air-Way s55 only (double-pass 27 rows); D@BORE: OMi WebsitePartsInfo2026.xlsx Items!X96 Side 2 ID = 0.44 (table had 0.41) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]</t>
+          <t>Air-Way s55 only (double-pass 27 rows); D@BORE: OMi WebsitePartsInfo2026.xlsx Items!X96 Side 2 ID = 0.44 (table had 0.41) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; C1HEX@HEX: OMi WebsitePartsInfo2026.xlsx Items!R96 = 1 (table had 0.94) [user 2026-10-18 A19]</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>A20 (user 2026-10-18): W@HEX 1.75 -&gt; OMi 1.70 (Items!L96; nut face at OMi's overall length) | A21 (user 2026-10-18): D@BORE 0.44 (OMi, batch 14) -&gt; Air-Way 0.41 (0.41 (07_RAW_EXTRACTS\1404.csv col 9 (D))) | A19 (user 2026-10-18, group 3 open): C1HEX@HEX 0.94 -&gt; OMi 1 (Items!R96, M051)</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
@@ -1181,7 +1226,7 @@
         <v>1.56</v>
       </c>
       <c r="C14" t="n">
-        <v>1.81</v>
+        <v>1.77</v>
       </c>
       <c r="D14" t="n">
         <v>0.88</v>
@@ -1193,7 +1238,7 @@
         <v>0.53</v>
       </c>
       <c r="G14" t="n">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="H14" t="n">
         <v>0.84</v>
@@ -1221,6 +1266,11 @@
           <t>Air-Way s55 only (double-pass 27 rows); D@BORE: OMi WebsitePartsInfo2026.xlsx Items!X97 Side 2 ID = 0.32 (table had 0.33) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]</t>
         </is>
       </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>A20 (user 2026-10-18): W@HEX 1.81 -&gt; OMi 1.77 (Items!L97; nut face at OMi's overall length) | A21 (user 2026-10-18): D@BORE 0.32 (OMi, batch 14) -&gt; Air-Way 0.33 (0.33 (07_RAW_EXTRACTS\1404.csv col 9 (D)))</t>
+        </is>
+      </c>
       <c r="O14" t="inlineStr">
         <is>
           <t>BUILD</t>
@@ -1242,10 +1292,10 @@
         <v>1.61</v>
       </c>
       <c r="C15" t="n">
-        <v>1.94</v>
+        <v>1.89</v>
       </c>
       <c r="D15" t="n">
-        <v>0.9399999999999999</v>
+        <v>1</v>
       </c>
       <c r="E15" t="n">
         <v>1</v>
@@ -1254,7 +1304,7 @@
         <v>0.53</v>
       </c>
       <c r="G15" t="n">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="H15" t="n">
         <v>0.84</v>
@@ -1279,7 +1329,12 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>Air-Way s55 only (double-pass 27 rows); D@BORE: OMi WebsitePartsInfo2026.xlsx Items!X98 Side 2 ID = 0.44 (table had 0.45) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]</t>
+          <t>Air-Way s55 only (double-pass 27 rows); D@BORE: OMi WebsitePartsInfo2026.xlsx Items!X98 Side 2 ID = 0.44 (table had 0.45) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; C1HEX@HEX: OMi WebsitePartsInfo2026.xlsx Items!R98 = 1 (table had 0.94) [user 2026-10-18 A19]</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>A20 (user 2026-10-18): W@HEX 1.94 -&gt; OMi 1.89 (Items!L98; nut face at OMi's overall length) | A21 (user 2026-10-18): D@BORE 0.44 (OMi, batch 14) -&gt; Air-Way 0.45 (0.45 (07_RAW_EXTRACTS\1404.csv col 9 (D))) | A19 (user 2026-10-18, group 3 open): C1HEX@HEX 0.94 -&gt; OMi 1 (Items!R98, M051)</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
@@ -1303,10 +1358,10 @@
         <v>1.73</v>
       </c>
       <c r="C16" t="n">
-        <v>2.06</v>
+        <v>2.09</v>
       </c>
       <c r="D16" t="n">
-        <v>1.13</v>
+        <v>1.25</v>
       </c>
       <c r="E16" t="n">
         <v>1.25</v>
@@ -1315,7 +1370,7 @@
         <v>0.53</v>
       </c>
       <c r="G16" t="n">
-        <v>0.61</v>
+        <v>0.53</v>
       </c>
       <c r="H16" t="n">
         <v>0.84</v>
@@ -1340,7 +1395,12 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>Air-Way s55 only (double-pass 27 rows); D@BORE: OMi WebsitePartsInfo2026.xlsx Items!X99 Side 2 ID = 0.61 (table had 0.53) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]</t>
+          <t>Air-Way s55 only (double-pass 27 rows); D@BORE: OMi WebsitePartsInfo2026.xlsx Items!X99 Side 2 ID = 0.61 (table had 0.53) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; C1HEX@HEX: OMi WebsitePartsInfo2026.xlsx Items!R99 = 1.250 (table had 1.13) [user 2026-10-18 A19]</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>A20 (user 2026-10-18): W@HEX 2.06 -&gt; OMi 2.09 (Items!L99; nut face at OMi's overall length) | A21 (user 2026-10-18): D@BORE 0.61 (OMi, batch 14) -&gt; Air-Way 0.53 (0.53 (07_RAW_EXTRACTS\1404.csv col 9 (D))) | A19 (user 2026-10-18, group 3 open): C1HEX@HEX 1.13 -&gt; OMi 1.250 (Items!R99, M051)</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
@@ -1364,7 +1424,7 @@
         <v>1.62</v>
       </c>
       <c r="C17" t="n">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="D17" t="n">
         <v>1.13</v>
@@ -1376,7 +1436,7 @@
         <v>0.72</v>
       </c>
       <c r="G17" t="n">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="H17" t="n">
         <v>1.05</v>
@@ -1404,6 +1464,11 @@
           <t>Air-Way s55 only (double-pass 27 rows); D@BORE: OMi WebsitePartsInfo2026.xlsx Items!X100 Side 2 ID = 0.44 (table had 0.45) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]</t>
         </is>
       </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>A20 (user 2026-10-18): W@HEX 1.95 -&gt; OMi 1.93 (Items!L100; nut face at OMi's overall length) | A21 (user 2026-10-18): D@BORE 0.44 (OMi, batch 14) -&gt; Air-Way 0.45 (0.45 (07_RAW_EXTRACTS\1404.csv col 9 (D)))</t>
+        </is>
+      </c>
       <c r="O17" t="inlineStr">
         <is>
           <t>BUILD</t>
@@ -1425,19 +1490,19 @@
         <v>1.73</v>
       </c>
       <c r="C18" t="n">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="D18" t="n">
-        <v>1.13</v>
+        <v>1.25</v>
       </c>
       <c r="E18" t="n">
         <v>1.25</v>
       </c>
       <c r="F18" t="n">
-        <v>0.61</v>
+        <v>0.72</v>
       </c>
       <c r="G18" t="n">
-        <v>0.61</v>
+        <v>0.63</v>
       </c>
       <c r="H18" t="n">
         <v>1.05</v>
@@ -1462,7 +1527,12 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>Air-Way s55 only (double-pass 27 rows); D2@BORE: OMi WebsitePartsInfo2026.xlsx Items!S101 Side 1 ID = 0.610 (table had 0.72); D@BORE: OMi WebsitePartsInfo2026.xlsx Items!X101 Side 2 ID = 0.61 (table had 0.63) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]</t>
+          <t>Air-Way s55 only (double-pass 27 rows); D2@BORE: OMi WebsitePartsInfo2026.xlsx Items!S101 Side 1 ID = 0.610 (table had 0.72); D@BORE: OMi WebsitePartsInfo2026.xlsx Items!X101 Side 2 ID = 0.61 (table had 0.63) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; C1HEX@HEX: OMi WebsitePartsInfo2026.xlsx Items!R101 = 1.250 (table had 1.13) [user 2026-10-18 A19]</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>A20 (user 2026-10-18): W@HEX 2.06 -&gt; OMi 2.10 (Items!L101; nut face at OMi's overall length) | A21 (user 2026-10-18): D@BORE 0.61 (OMi, batch 14) -&gt; Air-Way 0.63 (0.63 (07_RAW_EXTRACTS\1404.csv col 9 (D))) | A21 (user 2026-10-18): D2@BORE 0.61 (OMi, batch 14) -&gt; Air-Way 0.72 (0.72 (07_RAW_EXTRACTS\1404.csv col 8 (D2))) | A19 (user 2026-10-18, group 3 open): C1HEX@HEX 1.13 -&gt; OMi 1.250 (Items!R101, M051)</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
@@ -1486,7 +1556,7 @@
         <v>1.81</v>
       </c>
       <c r="C19" t="n">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="D19" t="n">
         <v>1.5</v>
@@ -1498,7 +1568,7 @@
         <v>0.72</v>
       </c>
       <c r="G19" t="n">
-        <v>0.78</v>
+        <v>0.72</v>
       </c>
       <c r="H19" t="n">
         <v>1.05</v>
@@ -1526,6 +1596,11 @@
           <t>Air-Way s55 only (double-pass 27 rows); D@BORE: OMi WebsitePartsInfo2026.xlsx Items!X102 Side 2 ID = 0.78 (table had 0.72) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]</t>
         </is>
       </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>A20 (user 2026-10-18): W@HEX 2.18 -&gt; OMi 2.16 (Items!L102; nut face at OMi's overall length) | A21 (user 2026-10-18): D@BORE 0.78 (OMi, batch 14) -&gt; Air-Way 0.72 (0.72 (07_RAW_EXTRACTS\1404.csv col 9 (D)))</t>
+        </is>
+      </c>
       <c r="O19" t="inlineStr">
         <is>
           <t>BUILD</t>
@@ -1550,7 +1625,7 @@
         <v>2.31</v>
       </c>
       <c r="D20" t="n">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="E20" t="n">
         <v>1.25</v>
@@ -1559,7 +1634,7 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="G20" t="n">
-        <v>0.61</v>
+        <v>0.63</v>
       </c>
       <c r="H20" t="n">
         <v>1.315</v>
@@ -1584,7 +1659,12 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>Air-Way s55 only (double-pass 27 rows); D@BORE: OMi WebsitePartsInfo2026.xlsx Items!X103 Side 2 ID = 0.61 (table had 0.63) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]</t>
+          <t>Air-Way s55 only (double-pass 27 rows); D@BORE: OMi WebsitePartsInfo2026.xlsx Items!X103 Side 2 ID = 0.61 (table had 0.63) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; C1HEX@HEX: OMi WebsitePartsInfo2026.xlsx Items!R103 = 1.500 (table had 1.38) [user 2026-10-18 A19]</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>A20 (user 2026-10-18): W@HEX 2.31 -&gt; OMi 2.29 (Items!L103; nut face at OMi's overall length) | A21 (user 2026-10-18): D@BORE 0.61 (OMi, batch 14) -&gt; Air-Way 0.63 (0.63 (07_RAW_EXTRACTS\1404.csv col 9 (D))) | A19 (user 2026-10-18, group 3 open): C1HEX@HEX 1.38 -&gt; OMi 1.500 (Items!R103, M051) | A20 HELD (2026-10-18): OMi overall length 2.29 as nut face breaks the measured NPSM swivel (W-L out of range; OMi gives no stem-tip length to pair) -&gt; kept at Air-Way W 2.31; user 2026-10-18: keep Air-Way W, reported to OMi (10_DRAWINGS/for_OMi_LATER)</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
@@ -1608,7 +1688,7 @@
         <v>2</v>
       </c>
       <c r="C21" t="n">
-        <v>2.38</v>
+        <v>2.35</v>
       </c>
       <c r="D21" t="n">
         <v>1.5</v>
@@ -1620,7 +1700,7 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="G21" t="n">
-        <v>0.78</v>
+        <v>0.84</v>
       </c>
       <c r="H21" t="n">
         <v>1.315</v>
@@ -1648,6 +1728,11 @@
           <t>Air-Way s55 only (double-pass 27 rows); D@BORE: OMi WebsitePartsInfo2026.xlsx Items!X104 Side 2 ID = 0.78 (table had 0.84) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]</t>
         </is>
       </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>A20 (user 2026-10-18): W@HEX 2.38 -&gt; OMi 2.35 (Items!L104; nut face at OMi's overall length) | A21 (user 2026-10-18): D@BORE 0.78 (OMi, batch 14) -&gt; Air-Way 0.84 (0.84 (07_RAW_EXTRACTS\1404.csv col 9 (D)))</t>
+        </is>
+      </c>
       <c r="O21" t="inlineStr">
         <is>
           <t>BUILD</t>
@@ -1669,10 +1754,10 @@
         <v>2.03</v>
       </c>
       <c r="C22" t="n">
-        <v>2.46</v>
+        <v>2.47</v>
       </c>
       <c r="D22" t="n">
-        <v>1.75</v>
+        <v>1.875</v>
       </c>
       <c r="E22" t="n">
         <v>1.88</v>
@@ -1706,7 +1791,12 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>Air-Way s55 only (double-pass 27 rows)</t>
+          <t>Air-Way s55 only (double-pass 27 rows); C1HEX@HEX: OMi WebsitePartsInfo2026.xlsx Items!R105 = 1.875 (table had 1.75) [user 2026-10-18 A19]</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>A20 (user 2026-10-18): W@HEX 2.46 -&gt; OMi 2.47 (Items!L105; nut face at OMi's overall length) | A19 (user 2026-10-18, group 3 open): C1HEX@HEX 1.75 -&gt; OMi 1.875 (Items!R105, M051)</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
@@ -1730,10 +1820,10 @@
         <v>2</v>
       </c>
       <c r="C23" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="D23" t="n">
-        <v>1.75</v>
+        <v>1.875</v>
       </c>
       <c r="E23" t="n">
         <v>1.5</v>
@@ -1742,7 +1832,7 @@
         <v>1.25</v>
       </c>
       <c r="G23" t="n">
-        <v>0.78</v>
+        <v>0.84</v>
       </c>
       <c r="H23" t="n">
         <v>1.66</v>
@@ -1767,7 +1857,12 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>Air-Way s55 only (double-pass 27 rows); D@BORE: OMi WebsitePartsInfo2026.xlsx Items!X106 Side 2 ID = 0.78 (table had 0.84) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]</t>
+          <t>Air-Way s55 only (double-pass 27 rows); D@BORE: OMi WebsitePartsInfo2026.xlsx Items!X106 Side 2 ID = 0.78 (table had 0.84) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; C1HEX@HEX: OMi WebsitePartsInfo2026.xlsx Items!R106 = 1.875 (table had 1.75) [user 2026-10-18 A19]</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>A20 (user 2026-10-18): W@HEX 2.38 -&gt; OMi 2.40 (Items!L106; nut face at OMi's overall length) | A21 (user 2026-10-18): D@BORE 0.78 (OMi, batch 14) -&gt; Air-Way 0.84 (0.84 (07_RAW_EXTRACTS\1404.csv col 9 (D))) | A19 (user 2026-10-18, group 3 open): C1HEX@HEX 1.75 -&gt; OMi 1.875 (Items!R106, M051)</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
@@ -1791,10 +1886,10 @@
         <v>2.06</v>
       </c>
       <c r="C24" t="n">
-        <v>2.49</v>
+        <v>2.52</v>
       </c>
       <c r="D24" t="n">
-        <v>1.75</v>
+        <v>1.875</v>
       </c>
       <c r="E24" t="n">
         <v>1.88</v>
@@ -1828,7 +1923,12 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>Air-Way s55 only (double-pass 27 rows)</t>
+          <t>Air-Way s55 only (double-pass 27 rows); C1HEX@HEX: OMi WebsitePartsInfo2026.xlsx Items!R107 = 1.875 (table had 1.75) [user 2026-10-18 A19]</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>A20 (user 2026-10-18): W@HEX 2.49 -&gt; OMi 2.52 (Items!L107; nut face at OMi's overall length) | A19 (user 2026-10-18, group 3 open): C1HEX@HEX 1.75 -&gt; OMi 1.875 (Items!R107, M051)</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
@@ -1892,6 +1992,11 @@
           <t>Air-Way s55 only (double-pass 27 rows)</t>
         </is>
       </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>A20 (user 2026-10-18): W@HEX 2.51 -&gt; OMi 2.47 (Items!L108; nut face at OMi's overall length) | A20 HELD (2026-10-18): OMi overall length 2.47 as nut face breaks the measured NPSM swivel (W-L out of range; OMi gives no stem-tip length to pair) -&gt; kept at Air-Way W 2.51; user 2026-10-18: keep Air-Way W, reported to OMi (10_DRAWINGS/for_OMi_LATER)</t>
+        </is>
+      </c>
       <c r="O25" t="inlineStr">
         <is>
           <t>BUILD</t>
@@ -1916,7 +2021,7 @@
         <v>2.61</v>
       </c>
       <c r="D26" t="n">
-        <v>2</v>
+        <v>2.125</v>
       </c>
       <c r="E26" t="n">
         <v>1.88</v>
@@ -1950,7 +2055,12 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>Air-Way s55 only (double-pass 27 rows)</t>
+          <t>Air-Way s55 only (double-pass 27 rows); C1HEX@HEX: OMi WebsitePartsInfo2026.xlsx Items!R109 = 2.125 (table had 2) [user 2026-10-18 A19]</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>A20 (user 2026-10-18): W@HEX 2.61 -&gt; OMi 2.54 (Items!L109; nut face at OMi's overall length) | A19 (user 2026-10-18, group 3 open): C1HEX@HEX 2 -&gt; OMi 2.125 (Items!R109, M051) | A20 HELD (2026-10-18): OMi overall length 2.54 as nut face breaks the measured NPSM swivel (W-L out of range; OMi gives no stem-tip length to pair) -&gt; kept at Air-Way W 2.61; user 2026-10-18: keep Air-Way W, reported to OMi (10_DRAWINGS/for_OMi_LATER)</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
@@ -1974,7 +2084,7 @@
         <v>2.13</v>
       </c>
       <c r="C27" t="n">
-        <v>2.55</v>
+        <v>2.69</v>
       </c>
       <c r="D27" t="n">
         <v>2.13</v>
@@ -1986,7 +2096,7 @@
         <v>1.5</v>
       </c>
       <c r="G27" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="H27" t="n">
         <v>1.9</v>
@@ -2012,6 +2122,11 @@
       <c r="M27" t="inlineStr">
         <is>
           <t>Air-Way s55 only (double-pass 27 rows); D@BORE: OMi WebsitePartsInfo2026.xlsx Items!X110 Side 2 ID = 1.25 (table had 1.26) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>A20 (user 2026-10-18): W@HEX 2.55 -&gt; OMi 2.69 (Items!L110; nut face at OMi's overall length) | A21 (user 2026-10-18): D@BORE 1.25 (OMi, batch 14) -&gt; Air-Way 1.26 (1.26 (07_RAW_EXTRACTS\1404.csv col 9 (D)))</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">

--- a/04_DESIGN_TABLES/DesignTable_1404.xlsx
+++ b/04_DESIGN_TABLES/DesignTable_1404.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -513,7 +513,7 @@
         <v>1.15</v>
       </c>
       <c r="D3" t="n">
-        <v>0.5620000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="E3" t="n">
         <v>0.5600000000000001</v>
@@ -547,12 +547,12 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>Air-Way s55 only (double-pass 27 rows); D@BORE: OMi WebsitePartsInfo2026.xlsx Items!X88 Side 2 ID = 0.110 (table had 0.13) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; C1HEX@HEX: OMi WebsitePartsInfo2026.xlsx Items!R88 = 0.562 (table had 0.5) [user 2026-10-18 A19]</t>
+          <t>Air-Way s55 only (double-pass 27 rows); D@BORE: OMi WebsitePartsInfo2026.xlsx Items!X88 Side 2 ID = 0.110 (table had 0.13) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; C1HEX@HEX: OMi WebsitePartsInfo2026.xlsx Items!R88 = 0.562 (table had 0.5) [user 2026-10-18 A19]; C1HEX@HEX: Air-Way 0.5 (raw 07_RAW_EXTRACTS; OMi file / Brennan 0.562) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)]</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>A20 (user 2026-10-18): W@HEX 1.15 -&gt; OMi 1.08 (Items!L88; nut face at OMi's overall length) | A21 (user 2026-10-18): D@BORE 0.11 (OMi, batch 14) -&gt; Air-Way 0.13 (0.13 (07_RAW_EXTRACTS\1404.csv col 9 (D))) | A19 (user 2026-10-18, group 3 open): C1HEX@HEX 0.5 -&gt; OMi 0.562 (Items!R88, M051) | A20 HELD (2026-10-18): OMi overall length 1.08 as nut face breaks the measured NPSM swivel (W-L out of range; OMi gives no stem-tip length to pair) -&gt; kept at Air-Way W 1.15; user 2026-10-18: keep Air-Way W, reported to OMi (10_DRAWINGS/for_OMi_LATER)</t>
+          <t>A20 (user 2026-10-18): W@HEX 1.15 -&gt; OMi 1.08 (Items!L88; nut face at OMi's overall length) | A21 (user 2026-10-18): D@BORE 0.11 (OMi, batch 14) -&gt; Air-Way 0.13 (0.13 (07_RAW_EXTRACTS\1404.csv col 9 (D))) | A19 (user 2026-10-18, group 3 open): C1HEX@HEX 0.5 -&gt; OMi 0.562 (Items!R88, M051) | A20 HELD (2026-10-18): OMi overall length 1.08 as nut face breaks the measured NPSM swivel (W-L out of range; OMi gives no stem-tip length to pair) -&gt; kept at Air-Way W 1.15; user 2026-10-18: keep Air-Way W, reported to OMi (10_DRAWINGS/for_OMi_LATER) | 2026-10-20 Air-Way first: C1HEX@HEX OMi/Brennan 0.562 -&gt; Air-Way 0.5</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -576,10 +576,10 @@
         <v>1.06</v>
       </c>
       <c r="C4" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="D4" t="n">
-        <v>0.6879999999999999</v>
+        <v>0.63</v>
       </c>
       <c r="E4" t="n">
         <v>0.6899999999999999</v>
@@ -613,12 +613,12 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>Air-Way s55 only (double-pass 27 rows); D@BORE: OMi WebsitePartsInfo2026.xlsx Items!X89 Side 2 ID = 0.21 (table had 0.19) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; C1HEX@HEX: OMi WebsitePartsInfo2026.xlsx Items!R89 = 0.688 (table had 0.63) [user 2026-10-18 A19]</t>
+          <t>Air-Way s55 only (double-pass 27 rows); D@BORE: OMi WebsitePartsInfo2026.xlsx Items!X89 Side 2 ID = 0.21 (table had 0.19) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; C1HEX@HEX: OMi WebsitePartsInfo2026.xlsx Items!R89 = 0.688 (table had 0.63) [user 2026-10-18 A19]; W@HEX: Air-Way 1.25 (raw 07_RAW_EXTRACTS; OMi file / Brennan 1.24) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)]; C1HEX@HEX: Air-Way 0.63 (raw 07_RAW_EXTRACTS; OMi file / Brennan 0.688) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)]</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>A20 (user 2026-10-18): W@HEX 1.25 -&gt; OMi 1.24 (Items!L89; nut face at OMi's overall length) | A21 (user 2026-10-18): D@BORE 0.21 (OMi, batch 14) -&gt; Air-Way 0.19 (0.19 (07_RAW_EXTRACTS\1404.csv col 9 (D))) | A19 (user 2026-10-18, group 3 open): C1HEX@HEX 0.63 -&gt; OMi 0.688 (Items!R89, M051)</t>
+          <t>A20 (user 2026-10-18): W@HEX 1.25 -&gt; OMi 1.24 (Items!L89; nut face at OMi's overall length) | A21 (user 2026-10-18): D@BORE 0.21 (OMi, batch 14) -&gt; Air-Way 0.19 (0.19 (07_RAW_EXTRACTS\1404.csv col 9 (D))) | A19 (user 2026-10-18, group 3 open): C1HEX@HEX 0.63 -&gt; OMi 0.688 (Items!R89, M051) | 2026-10-20 Air-Way first: W@HEX OMi/Brennan 1.24 -&gt; Air-Way 1.25 | 2026-10-20 Air-Way first: C1HEX@HEX OMi/Brennan 0.688 -&gt; Air-Way 0.63</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -703,10 +703,10 @@
         <v>1.19</v>
       </c>
       <c r="C6" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="D6" t="n">
-        <v>0.6879999999999999</v>
+        <v>0.63</v>
       </c>
       <c r="E6" t="n">
         <v>0.5600000000000001</v>
@@ -740,12 +740,12 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>Air-Way s55 only (double-pass 27 rows); C1HEX@HEX: OMi WebsitePartsInfo2026.xlsx Items!R90 = 0.688 (table had 0.63) [user 2026-10-18 A19]</t>
+          <t>Air-Way s55 only (double-pass 27 rows); C1HEX@HEX: OMi WebsitePartsInfo2026.xlsx Items!R90 = 0.688 (table had 0.63) [user 2026-10-18 A19]; W@HEX: Air-Way 1.34 (raw 07_RAW_EXTRACTS; OMi file / Brennan 1.33) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)]; C1HEX@HEX: Air-Way 0.63 (raw 07_RAW_EXTRACTS; OMi file / Brennan 0.688) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)]</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>A20 (user 2026-10-18): W@HEX 1.34 -&gt; OMi 1.33 (Items!L90; nut face at OMi's overall length) | A19 (user 2026-10-18, group 3 open): C1HEX@HEX 0.63 -&gt; OMi 0.688 (Items!R90, M051)</t>
+          <t>A20 (user 2026-10-18): W@HEX 1.34 -&gt; OMi 1.33 (Items!L90; nut face at OMi's overall length) | A19 (user 2026-10-18, group 3 open): C1HEX@HEX 0.63 -&gt; OMi 0.688 (Items!R90, M051) | 2026-10-20 Air-Way first: W@HEX OMi/Brennan 1.33 -&gt; Air-Way 1.34 | 2026-10-20 Air-Way first: C1HEX@HEX OMi/Brennan 0.688 -&gt; Air-Way 0.63</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -772,7 +772,7 @@
         <v>1.44</v>
       </c>
       <c r="D7" t="n">
-        <v>0.6879999999999999</v>
+        <v>0.63</v>
       </c>
       <c r="E7" t="n">
         <v>0.6899999999999999</v>
@@ -806,12 +806,12 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>Air-Way s55 only (double-pass 27 rows); D@BORE: OMi WebsitePartsInfo2026.xlsx Items!X91 Side 2 ID = 0.21 (table had 0.22) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; C1HEX@HEX: OMi WebsitePartsInfo2026.xlsx Items!R91 = 0.688 (table had 0.63) [user 2026-10-18 A19]</t>
+          <t>Air-Way s55 only (double-pass 27 rows); D@BORE: OMi WebsitePartsInfo2026.xlsx Items!X91 Side 2 ID = 0.21 (table had 0.22) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; C1HEX@HEX: OMi WebsitePartsInfo2026.xlsx Items!R91 = 0.688 (table had 0.63) [user 2026-10-18 A19]; C1HEX@HEX: Air-Way 0.63 (raw 07_RAW_EXTRACTS; OMi file / Brennan 0.688) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)]</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>A20 (user 2026-10-18): W@HEX 1.44 -&gt; OMi 1.42 (Items!L91; nut face at OMi's overall length) | A21 (user 2026-10-18): D@BORE 0.21 (OMi, batch 14) -&gt; Air-Way 0.22 (0.22 (07_RAW_EXTRACTS\1404.csv col 9 (D))) | A19 (user 2026-10-18, group 3 open): C1HEX@HEX 0.63 -&gt; OMi 0.688 (Items!R91, M051) | A20 HELD (2026-10-18): OMi overall length 1.42 as nut face breaks the measured NPSM swivel (W-L out of range; OMi gives no stem-tip length to pair) -&gt; kept at Air-Way W 1.44; user 2026-10-18: keep Air-Way W, reported to OMi (10_DRAWINGS/for_OMi_LATER)</t>
+          <t>A20 (user 2026-10-18): W@HEX 1.44 -&gt; OMi 1.42 (Items!L91; nut face at OMi's overall length) | A21 (user 2026-10-18): D@BORE 0.21 (OMi, batch 14) -&gt; Air-Way 0.22 (0.22 (07_RAW_EXTRACTS\1404.csv col 9 (D))) | A19 (user 2026-10-18, group 3 open): C1HEX@HEX 0.63 -&gt; OMi 0.688 (Items!R91, M051) | A20 HELD (2026-10-18): OMi overall length 1.42 as nut face breaks the measured NPSM swivel (W-L out of range; OMi gives no stem-tip length to pair) -&gt; kept at Air-Way W 1.44; user 2026-10-18: keep Air-Way W, reported to OMi (10_DRAWINGS/for_OMi_LATER) | 2026-10-20 Air-Way first: C1HEX@HEX OMi/Brennan 0.688 -&gt; Air-Way 0.63</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -835,7 +835,7 @@
         <v>1.31</v>
       </c>
       <c r="C8" t="n">
-        <v>1.52</v>
+        <v>1.56</v>
       </c>
       <c r="D8" t="n">
         <v>0.8100000000000001</v>
@@ -872,12 +872,12 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>Air-Way s55 only (double-pass 27 rows)</t>
+          <t>Air-Way s55 only (double-pass 27 rows); W@HEX: Air-Way 1.56 (raw 07_RAW_EXTRACTS; OMi file / Brennan 1.52) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)]</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>A20 (user 2026-10-18): W@HEX 1.56 -&gt; OMi 1.52 (Items!L92; nut face at OMi's overall length)</t>
+          <t>A20 (user 2026-10-18): W@HEX 1.56 -&gt; OMi 1.52 (Items!L92; nut face at OMi's overall length) | 2026-10-20 Air-Way first: W@HEX OMi/Brennan 1.52 -&gt; Air-Way 1.56</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -901,10 +901,10 @@
         <v>1.42</v>
       </c>
       <c r="C9" t="n">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="D9" t="n">
-        <v>1</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="E9" t="n">
         <v>1</v>
@@ -938,12 +938,12 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>Air-Way s55 only (double-pass 27 rows); D@BORE: OMi WebsitePartsInfo2026.xlsx Items!X93 Side 2 ID = 0.44 (table had 0.28) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; C1HEX@HEX: OMi WebsitePartsInfo2026.xlsx Items!R93 = 1.000 (table had 0.94) [user 2026-10-18 A19]</t>
+          <t>Air-Way s55 only (double-pass 27 rows); D@BORE: OMi WebsitePartsInfo2026.xlsx Items!X93 Side 2 ID = 0.44 (table had 0.28) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; C1HEX@HEX: OMi WebsitePartsInfo2026.xlsx Items!R93 = 1.000 (table had 0.94) [user 2026-10-18 A19]; W@HEX: Air-Way 1.75 (raw 07_RAW_EXTRACTS; OMi file / Brennan 1.7) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)]; C1HEX@HEX: Air-Way 0.94 (raw 07_RAW_EXTRACTS; OMi file / Brennan 1) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)]</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>A20 (user 2026-10-18): W@HEX 1.75 -&gt; OMi 1.70 (Items!L93; nut face at OMi's overall length) | A21 (user 2026-10-18): D@BORE 0.44 (OMi, batch 14) -&gt; Air-Way 0.28 (0.28 (07_RAW_EXTRACTS\1404.csv col 9 (D))) | A19 (user 2026-10-18, group 3 open): C1HEX@HEX 0.94 -&gt; OMi 1.000 (Items!R93, M051)</t>
+          <t>A20 (user 2026-10-18): W@HEX 1.75 -&gt; OMi 1.70 (Items!L93; nut face at OMi's overall length) | A21 (user 2026-10-18): D@BORE 0.44 (OMi, batch 14) -&gt; Air-Way 0.28 (0.28 (07_RAW_EXTRACTS\1404.csv col 9 (D))) | A19 (user 2026-10-18, group 3 open): C1HEX@HEX 0.94 -&gt; OMi 1.000 (Items!R93, M051) | 2026-10-20 Air-Way first: W@HEX OMi/Brennan 1.7 -&gt; Air-Way 1.75 | 2026-10-20 Air-Way first: C1HEX@HEX OMi/Brennan 1 -&gt; Air-Way 0.94</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -967,7 +967,7 @@
         <v>1.31</v>
       </c>
       <c r="C10" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="D10" t="n">
         <v>0.75</v>
@@ -1004,12 +1004,12 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>Air-Way s55 only (double-pass 27 rows); D@BORE: OMi WebsitePartsInfo2026.xlsx Items!X94 Side 2 ID = 0.21 (table had 0.22) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]</t>
+          <t>Air-Way s55 only (double-pass 27 rows); D@BORE: OMi WebsitePartsInfo2026.xlsx Items!X94 Side 2 ID = 0.21 (table had 0.22) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; W@HEX: Air-Way 1.5 (raw 07_RAW_EXTRACTS; OMi file / Brennan 1.49) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)]</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>A20 (user 2026-10-18): W@HEX 1.5 -&gt; OMi 1.49 (Items!L94; nut face at OMi's overall length) | A21 (user 2026-10-18): D@BORE 0.21 (OMi, batch 14) -&gt; Air-Way 0.22 (0.22 (07_RAW_EXTRACTS\1404.csv col 9 (D)))</t>
+          <t>A20 (user 2026-10-18): W@HEX 1.5 -&gt; OMi 1.49 (Items!L94; nut face at OMi's overall length) | A21 (user 2026-10-18): D@BORE 0.21 (OMi, batch 14) -&gt; Air-Way 0.22 (0.22 (07_RAW_EXTRACTS\1404.csv col 9 (D))) | 2026-10-20 Air-Way first: W@HEX OMi/Brennan 1.49 -&gt; Air-Way 1.5</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -1033,10 +1033,10 @@
         <v>1.31</v>
       </c>
       <c r="C11" t="n">
-        <v>1.52</v>
+        <v>1.56</v>
       </c>
       <c r="D11" t="n">
-        <v>0.875</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="E11" t="n">
         <v>0.88</v>
@@ -1070,12 +1070,12 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>Air-Way s55 only (double-pass 27 rows); D@BORE: OMi WebsitePartsInfo2026.xlsx Items!X95 Side 2 ID = 0.32 (table had 0.33) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; C1HEX@HEX: OMi WebsitePartsInfo2026.xlsx Items!R95 = 0.875 (table had 0.81) [user 2026-10-18 A19]</t>
+          <t>Air-Way s55 only (double-pass 27 rows); D@BORE: OMi WebsitePartsInfo2026.xlsx Items!X95 Side 2 ID = 0.32 (table had 0.33) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; C1HEX@HEX: OMi WebsitePartsInfo2026.xlsx Items!R95 = 0.875 (table had 0.81) [user 2026-10-18 A19]; W@HEX: Air-Way 1.56 (raw 07_RAW_EXTRACTS; OMi file / Brennan 1.52) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)]; C1HEX@HEX: Air-Way 0.81 (raw 07_RAW_EXTRACTS; OMi file / Brennan 0.875) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)]</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>A20 (user 2026-10-18): W@HEX 1.56 -&gt; OMi 1.52 (Items!L95; nut face at OMi's overall length) | A21 (user 2026-10-18): D@BORE 0.32 (OMi, batch 14) -&gt; Air-Way 0.33 (0.33 (07_RAW_EXTRACTS\1404.csv col 9 (D))) | A19 (user 2026-10-18, group 3 open): C1HEX@HEX 0.81 -&gt; OMi 0.875 (Items!R95, M051)</t>
+          <t>A20 (user 2026-10-18): W@HEX 1.56 -&gt; OMi 1.52 (Items!L95; nut face at OMi's overall length) | A21 (user 2026-10-18): D@BORE 0.32 (OMi, batch 14) -&gt; Air-Way 0.33 (0.33 (07_RAW_EXTRACTS\1404.csv col 9 (D))) | A19 (user 2026-10-18, group 3 open): C1HEX@HEX 0.81 -&gt; OMi 0.875 (Items!R95, M051) | 2026-10-20 Air-Way first: W@HEX OMi/Brennan 1.52 -&gt; Air-Way 1.56 | 2026-10-20 Air-Way first: C1HEX@HEX OMi/Brennan 0.875 -&gt; Air-Way 0.81</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -1099,10 +1099,10 @@
         <v>1.42</v>
       </c>
       <c r="C12" t="n">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="D12" t="n">
-        <v>1</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="E12" t="n">
         <v>1</v>
@@ -1136,12 +1136,12 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>Air-Way s55 only (double-pass 27 rows); D@BORE: OMi WebsitePartsInfo2026.xlsx Items!X96 Side 2 ID = 0.44 (table had 0.41) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; C1HEX@HEX: OMi WebsitePartsInfo2026.xlsx Items!R96 = 1 (table had 0.94) [user 2026-10-18 A19]</t>
+          <t>Air-Way s55 only (double-pass 27 rows); D@BORE: OMi WebsitePartsInfo2026.xlsx Items!X96 Side 2 ID = 0.44 (table had 0.41) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; C1HEX@HEX: OMi WebsitePartsInfo2026.xlsx Items!R96 = 1 (table had 0.94) [user 2026-10-18 A19]; W@HEX: Air-Way 1.75 (raw 07_RAW_EXTRACTS; OMi file / Brennan 1.7) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)]; C1HEX@HEX: Air-Way 0.94 (raw 07_RAW_EXTRACTS; OMi file / Brennan 1) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)]</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>A20 (user 2026-10-18): W@HEX 1.75 -&gt; OMi 1.70 (Items!L96; nut face at OMi's overall length) | A21 (user 2026-10-18): D@BORE 0.44 (OMi, batch 14) -&gt; Air-Way 0.41 (0.41 (07_RAW_EXTRACTS\1404.csv col 9 (D))) | A19 (user 2026-10-18, group 3 open): C1HEX@HEX 0.94 -&gt; OMi 1 (Items!R96, M051)</t>
+          <t>A20 (user 2026-10-18): W@HEX 1.75 -&gt; OMi 1.70 (Items!L96; nut face at OMi's overall length) | A21 (user 2026-10-18): D@BORE 0.44 (OMi, batch 14) -&gt; Air-Way 0.41 (0.41 (07_RAW_EXTRACTS\1404.csv col 9 (D))) | A19 (user 2026-10-18, group 3 open): C1HEX@HEX 0.94 -&gt; OMi 1 (Items!R96, M051) | 2026-10-20 Air-Way first: W@HEX OMi/Brennan 1.7 -&gt; Air-Way 1.75 | 2026-10-20 Air-Way first: C1HEX@HEX OMi/Brennan 1 -&gt; Air-Way 0.94</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
@@ -1226,7 +1226,7 @@
         <v>1.56</v>
       </c>
       <c r="C14" t="n">
-        <v>1.77</v>
+        <v>1.81</v>
       </c>
       <c r="D14" t="n">
         <v>0.88</v>
@@ -1263,12 +1263,12 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>Air-Way s55 only (double-pass 27 rows); D@BORE: OMi WebsitePartsInfo2026.xlsx Items!X97 Side 2 ID = 0.32 (table had 0.33) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]</t>
+          <t>Air-Way s55 only (double-pass 27 rows); D@BORE: OMi WebsitePartsInfo2026.xlsx Items!X97 Side 2 ID = 0.32 (table had 0.33) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; W@HEX: Air-Way 1.81 (raw 07_RAW_EXTRACTS; OMi file / Brennan 1.77) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)]</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>A20 (user 2026-10-18): W@HEX 1.81 -&gt; OMi 1.77 (Items!L97; nut face at OMi's overall length) | A21 (user 2026-10-18): D@BORE 0.32 (OMi, batch 14) -&gt; Air-Way 0.33 (0.33 (07_RAW_EXTRACTS\1404.csv col 9 (D)))</t>
+          <t>A20 (user 2026-10-18): W@HEX 1.81 -&gt; OMi 1.77 (Items!L97; nut face at OMi's overall length) | A21 (user 2026-10-18): D@BORE 0.32 (OMi, batch 14) -&gt; Air-Way 0.33 (0.33 (07_RAW_EXTRACTS\1404.csv col 9 (D))) | 2026-10-20 Air-Way first: W@HEX OMi/Brennan 1.77 -&gt; Air-Way 1.81</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
@@ -1292,10 +1292,10 @@
         <v>1.61</v>
       </c>
       <c r="C15" t="n">
-        <v>1.89</v>
+        <v>1.94</v>
       </c>
       <c r="D15" t="n">
-        <v>1</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="E15" t="n">
         <v>1</v>
@@ -1329,12 +1329,12 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>Air-Way s55 only (double-pass 27 rows); D@BORE: OMi WebsitePartsInfo2026.xlsx Items!X98 Side 2 ID = 0.44 (table had 0.45) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; C1HEX@HEX: OMi WebsitePartsInfo2026.xlsx Items!R98 = 1 (table had 0.94) [user 2026-10-18 A19]</t>
+          <t>Air-Way s55 only (double-pass 27 rows); D@BORE: OMi WebsitePartsInfo2026.xlsx Items!X98 Side 2 ID = 0.44 (table had 0.45) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; C1HEX@HEX: OMi WebsitePartsInfo2026.xlsx Items!R98 = 1 (table had 0.94) [user 2026-10-18 A19]; W@HEX: Air-Way 1.94 (raw 07_RAW_EXTRACTS; OMi file / Brennan 1.89) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)]; C1HEX@HEX: Air-Way 0.94 (raw 07_RAW_EXTRACTS; OMi file / Brennan 1) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)]</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>A20 (user 2026-10-18): W@HEX 1.94 -&gt; OMi 1.89 (Items!L98; nut face at OMi's overall length) | A21 (user 2026-10-18): D@BORE 0.44 (OMi, batch 14) -&gt; Air-Way 0.45 (0.45 (07_RAW_EXTRACTS\1404.csv col 9 (D))) | A19 (user 2026-10-18, group 3 open): C1HEX@HEX 0.94 -&gt; OMi 1 (Items!R98, M051)</t>
+          <t>A20 (user 2026-10-18): W@HEX 1.94 -&gt; OMi 1.89 (Items!L98; nut face at OMi's overall length) | A21 (user 2026-10-18): D@BORE 0.44 (OMi, batch 14) -&gt; Air-Way 0.45 (0.45 (07_RAW_EXTRACTS\1404.csv col 9 (D))) | A19 (user 2026-10-18, group 3 open): C1HEX@HEX 0.94 -&gt; OMi 1 (Items!R98, M051) | 2026-10-20 Air-Way first: W@HEX OMi/Brennan 1.89 -&gt; Air-Way 1.94 | 2026-10-20 Air-Way first: C1HEX@HEX OMi/Brennan 1 -&gt; Air-Way 0.94</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
@@ -1358,10 +1358,10 @@
         <v>1.73</v>
       </c>
       <c r="C16" t="n">
-        <v>2.09</v>
+        <v>2.06</v>
       </c>
       <c r="D16" t="n">
-        <v>1.25</v>
+        <v>1.13</v>
       </c>
       <c r="E16" t="n">
         <v>1.25</v>
@@ -1395,12 +1395,12 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>Air-Way s55 only (double-pass 27 rows); D@BORE: OMi WebsitePartsInfo2026.xlsx Items!X99 Side 2 ID = 0.61 (table had 0.53) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; C1HEX@HEX: OMi WebsitePartsInfo2026.xlsx Items!R99 = 1.250 (table had 1.13) [user 2026-10-18 A19]</t>
+          <t>Air-Way s55 only (double-pass 27 rows); D@BORE: OMi WebsitePartsInfo2026.xlsx Items!X99 Side 2 ID = 0.61 (table had 0.53) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; C1HEX@HEX: OMi WebsitePartsInfo2026.xlsx Items!R99 = 1.250 (table had 1.13) [user 2026-10-18 A19]; W@HEX: Air-Way 2.06 (raw 07_RAW_EXTRACTS; OMi file / Brennan 2.09) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)]; C1HEX@HEX: Air-Way 1.13 (raw 07_RAW_EXTRACTS; OMi file / Brennan 1.25) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)]</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>A20 (user 2026-10-18): W@HEX 2.06 -&gt; OMi 2.09 (Items!L99; nut face at OMi's overall length) | A21 (user 2026-10-18): D@BORE 0.61 (OMi, batch 14) -&gt; Air-Way 0.53 (0.53 (07_RAW_EXTRACTS\1404.csv col 9 (D))) | A19 (user 2026-10-18, group 3 open): C1HEX@HEX 1.13 -&gt; OMi 1.250 (Items!R99, M051)</t>
+          <t>A20 (user 2026-10-18): W@HEX 2.06 -&gt; OMi 2.09 (Items!L99; nut face at OMi's overall length) | A21 (user 2026-10-18): D@BORE 0.61 (OMi, batch 14) -&gt; Air-Way 0.53 (0.53 (07_RAW_EXTRACTS\1404.csv col 9 (D))) | A19 (user 2026-10-18, group 3 open): C1HEX@HEX 1.13 -&gt; OMi 1.250 (Items!R99, M051) | 2026-10-20 Air-Way first: W@HEX OMi/Brennan 2.09 -&gt; Air-Way 2.06 | 2026-10-20 Air-Way first: C1HEX@HEX OMi/Brennan 1.25 -&gt; Air-Way 1.13</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
@@ -1424,7 +1424,7 @@
         <v>1.62</v>
       </c>
       <c r="C17" t="n">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="D17" t="n">
         <v>1.13</v>
@@ -1461,12 +1461,12 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>Air-Way s55 only (double-pass 27 rows); D@BORE: OMi WebsitePartsInfo2026.xlsx Items!X100 Side 2 ID = 0.44 (table had 0.45) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]</t>
+          <t>Air-Way s55 only (double-pass 27 rows); D@BORE: OMi WebsitePartsInfo2026.xlsx Items!X100 Side 2 ID = 0.44 (table had 0.45) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; W@HEX: Air-Way 1.95 (raw 07_RAW_EXTRACTS; OMi file / Brennan 1.93) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)]</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>A20 (user 2026-10-18): W@HEX 1.95 -&gt; OMi 1.93 (Items!L100; nut face at OMi's overall length) | A21 (user 2026-10-18): D@BORE 0.44 (OMi, batch 14) -&gt; Air-Way 0.45 (0.45 (07_RAW_EXTRACTS\1404.csv col 9 (D)))</t>
+          <t>A20 (user 2026-10-18): W@HEX 1.95 -&gt; OMi 1.93 (Items!L100; nut face at OMi's overall length) | A21 (user 2026-10-18): D@BORE 0.44 (OMi, batch 14) -&gt; Air-Way 0.45 (0.45 (07_RAW_EXTRACTS\1404.csv col 9 (D))) | 2026-10-20 Air-Way first: W@HEX OMi/Brennan 1.93 -&gt; Air-Way 1.95</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
@@ -1490,10 +1490,10 @@
         <v>1.73</v>
       </c>
       <c r="C18" t="n">
-        <v>2.1</v>
+        <v>2.06</v>
       </c>
       <c r="D18" t="n">
-        <v>1.25</v>
+        <v>1.13</v>
       </c>
       <c r="E18" t="n">
         <v>1.25</v>
@@ -1527,12 +1527,12 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>Air-Way s55 only (double-pass 27 rows); D2@BORE: OMi WebsitePartsInfo2026.xlsx Items!S101 Side 1 ID = 0.610 (table had 0.72); D@BORE: OMi WebsitePartsInfo2026.xlsx Items!X101 Side 2 ID = 0.61 (table had 0.63) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; C1HEX@HEX: OMi WebsitePartsInfo2026.xlsx Items!R101 = 1.250 (table had 1.13) [user 2026-10-18 A19]</t>
+          <t>Air-Way s55 only (double-pass 27 rows); D2@BORE: OMi WebsitePartsInfo2026.xlsx Items!S101 Side 1 ID = 0.610 (table had 0.72); D@BORE: OMi WebsitePartsInfo2026.xlsx Items!X101 Side 2 ID = 0.61 (table had 0.63) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; C1HEX@HEX: OMi WebsitePartsInfo2026.xlsx Items!R101 = 1.250 (table had 1.13) [user 2026-10-18 A19]; W@HEX: Air-Way 2.06 (raw 07_RAW_EXTRACTS; OMi file / Brennan 2.1) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)]; C1HEX@HEX: Air-Way 1.13 (raw 07_RAW_EXTRACTS; OMi file / Brennan 1.25) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)]</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>A20 (user 2026-10-18): W@HEX 2.06 -&gt; OMi 2.10 (Items!L101; nut face at OMi's overall length) | A21 (user 2026-10-18): D@BORE 0.61 (OMi, batch 14) -&gt; Air-Way 0.63 (0.63 (07_RAW_EXTRACTS\1404.csv col 9 (D))) | A21 (user 2026-10-18): D2@BORE 0.61 (OMi, batch 14) -&gt; Air-Way 0.72 (0.72 (07_RAW_EXTRACTS\1404.csv col 8 (D2))) | A19 (user 2026-10-18, group 3 open): C1HEX@HEX 1.13 -&gt; OMi 1.250 (Items!R101, M051)</t>
+          <t>A20 (user 2026-10-18): W@HEX 2.06 -&gt; OMi 2.10 (Items!L101; nut face at OMi's overall length) | A21 (user 2026-10-18): D@BORE 0.61 (OMi, batch 14) -&gt; Air-Way 0.63 (0.63 (07_RAW_EXTRACTS\1404.csv col 9 (D))) | A21 (user 2026-10-18): D2@BORE 0.61 (OMi, batch 14) -&gt; Air-Way 0.72 (0.72 (07_RAW_EXTRACTS\1404.csv col 8 (D2))) | A19 (user 2026-10-18, group 3 open): C1HEX@HEX 1.13 -&gt; OMi 1.250 (Items!R101, M051) | 2026-10-20 Air-Way first: W@HEX OMi/Brennan 2.1 -&gt; Air-Way 2.06 | 2026-10-20 Air-Way first: C1HEX@HEX OMi/Brennan 1.25 -&gt; Air-Way 1.13</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
@@ -1556,7 +1556,7 @@
         <v>1.81</v>
       </c>
       <c r="C19" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="D19" t="n">
         <v>1.5</v>
@@ -1593,12 +1593,12 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>Air-Way s55 only (double-pass 27 rows); D@BORE: OMi WebsitePartsInfo2026.xlsx Items!X102 Side 2 ID = 0.78 (table had 0.72) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]</t>
+          <t>Air-Way s55 only (double-pass 27 rows); D@BORE: OMi WebsitePartsInfo2026.xlsx Items!X102 Side 2 ID = 0.78 (table had 0.72) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; W@HEX: Air-Way 2.18 (raw 07_RAW_EXTRACTS; OMi file / Brennan 2.16) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)]</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>A20 (user 2026-10-18): W@HEX 2.18 -&gt; OMi 2.16 (Items!L102; nut face at OMi's overall length) | A21 (user 2026-10-18): D@BORE 0.78 (OMi, batch 14) -&gt; Air-Way 0.72 (0.72 (07_RAW_EXTRACTS\1404.csv col 9 (D)))</t>
+          <t>A20 (user 2026-10-18): W@HEX 2.18 -&gt; OMi 2.16 (Items!L102; nut face at OMi's overall length) | A21 (user 2026-10-18): D@BORE 0.78 (OMi, batch 14) -&gt; Air-Way 0.72 (0.72 (07_RAW_EXTRACTS\1404.csv col 9 (D))) | 2026-10-20 Air-Way first: W@HEX OMi/Brennan 2.16 -&gt; Air-Way 2.18</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
@@ -1625,7 +1625,7 @@
         <v>2.31</v>
       </c>
       <c r="D20" t="n">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="E20" t="n">
         <v>1.25</v>
@@ -1659,12 +1659,12 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>Air-Way s55 only (double-pass 27 rows); D@BORE: OMi WebsitePartsInfo2026.xlsx Items!X103 Side 2 ID = 0.61 (table had 0.63) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; C1HEX@HEX: OMi WebsitePartsInfo2026.xlsx Items!R103 = 1.500 (table had 1.38) [user 2026-10-18 A19]</t>
+          <t>Air-Way s55 only (double-pass 27 rows); D@BORE: OMi WebsitePartsInfo2026.xlsx Items!X103 Side 2 ID = 0.61 (table had 0.63) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; C1HEX@HEX: OMi WebsitePartsInfo2026.xlsx Items!R103 = 1.500 (table had 1.38) [user 2026-10-18 A19]; C1HEX@HEX: Air-Way 1.38 (raw 07_RAW_EXTRACTS; OMi file / Brennan 1.5) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)]</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>A20 (user 2026-10-18): W@HEX 2.31 -&gt; OMi 2.29 (Items!L103; nut face at OMi's overall length) | A21 (user 2026-10-18): D@BORE 0.61 (OMi, batch 14) -&gt; Air-Way 0.63 (0.63 (07_RAW_EXTRACTS\1404.csv col 9 (D))) | A19 (user 2026-10-18, group 3 open): C1HEX@HEX 1.38 -&gt; OMi 1.500 (Items!R103, M051) | A20 HELD (2026-10-18): OMi overall length 2.29 as nut face breaks the measured NPSM swivel (W-L out of range; OMi gives no stem-tip length to pair) -&gt; kept at Air-Way W 2.31; user 2026-10-18: keep Air-Way W, reported to OMi (10_DRAWINGS/for_OMi_LATER)</t>
+          <t>A20 (user 2026-10-18): W@HEX 2.31 -&gt; OMi 2.29 (Items!L103; nut face at OMi's overall length) | A21 (user 2026-10-18): D@BORE 0.61 (OMi, batch 14) -&gt; Air-Way 0.63 (0.63 (07_RAW_EXTRACTS\1404.csv col 9 (D))) | A19 (user 2026-10-18, group 3 open): C1HEX@HEX 1.38 -&gt; OMi 1.500 (Items!R103, M051) | A20 HELD (2026-10-18): OMi overall length 2.29 as nut face breaks the measured NPSM swivel (W-L out of range; OMi gives no stem-tip length to pair) -&gt; kept at Air-Way W 2.31; user 2026-10-18: keep Air-Way W, reported to OMi (10_DRAWINGS/for_OMi_LATER) | 2026-10-20 Air-Way first: C1HEX@HEX OMi/Brennan 1.5 -&gt; Air-Way 1.38</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
@@ -1688,7 +1688,7 @@
         <v>2</v>
       </c>
       <c r="C21" t="n">
-        <v>2.35</v>
+        <v>2.38</v>
       </c>
       <c r="D21" t="n">
         <v>1.5</v>
@@ -1725,12 +1725,12 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>Air-Way s55 only (double-pass 27 rows); D@BORE: OMi WebsitePartsInfo2026.xlsx Items!X104 Side 2 ID = 0.78 (table had 0.84) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]</t>
+          <t>Air-Way s55 only (double-pass 27 rows); D@BORE: OMi WebsitePartsInfo2026.xlsx Items!X104 Side 2 ID = 0.78 (table had 0.84) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; W@HEX: Air-Way 2.38 (raw 07_RAW_EXTRACTS; OMi file / Brennan 2.35) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)]</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>A20 (user 2026-10-18): W@HEX 2.38 -&gt; OMi 2.35 (Items!L104; nut face at OMi's overall length) | A21 (user 2026-10-18): D@BORE 0.78 (OMi, batch 14) -&gt; Air-Way 0.84 (0.84 (07_RAW_EXTRACTS\1404.csv col 9 (D)))</t>
+          <t>A20 (user 2026-10-18): W@HEX 2.38 -&gt; OMi 2.35 (Items!L104; nut face at OMi's overall length) | A21 (user 2026-10-18): D@BORE 0.78 (OMi, batch 14) -&gt; Air-Way 0.84 (0.84 (07_RAW_EXTRACTS\1404.csv col 9 (D))) | 2026-10-20 Air-Way first: W@HEX OMi/Brennan 2.35 -&gt; Air-Way 2.38</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
@@ -1754,10 +1754,10 @@
         <v>2.03</v>
       </c>
       <c r="C22" t="n">
-        <v>2.47</v>
+        <v>2.46</v>
       </c>
       <c r="D22" t="n">
-        <v>1.875</v>
+        <v>1.75</v>
       </c>
       <c r="E22" t="n">
         <v>1.88</v>
@@ -1791,12 +1791,12 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>Air-Way s55 only (double-pass 27 rows); C1HEX@HEX: OMi WebsitePartsInfo2026.xlsx Items!R105 = 1.875 (table had 1.75) [user 2026-10-18 A19]</t>
+          <t>Air-Way s55 only (double-pass 27 rows); C1HEX@HEX: OMi WebsitePartsInfo2026.xlsx Items!R105 = 1.875 (table had 1.75) [user 2026-10-18 A19]; W@HEX: Air-Way 2.46 (raw 07_RAW_EXTRACTS; OMi file / Brennan 2.47) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)]; C1HEX@HEX: Air-Way 1.75 (raw 07_RAW_EXTRACTS; OMi file / Brennan 1.875) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)]</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>A20 (user 2026-10-18): W@HEX 2.46 -&gt; OMi 2.47 (Items!L105; nut face at OMi's overall length) | A19 (user 2026-10-18, group 3 open): C1HEX@HEX 1.75 -&gt; OMi 1.875 (Items!R105, M051)</t>
+          <t>A20 (user 2026-10-18): W@HEX 2.46 -&gt; OMi 2.47 (Items!L105; nut face at OMi's overall length) | A19 (user 2026-10-18, group 3 open): C1HEX@HEX 1.75 -&gt; OMi 1.875 (Items!R105, M051) | 2026-10-20 Air-Way first: W@HEX OMi/Brennan 2.47 -&gt; Air-Way 2.46 | 2026-10-20 Air-Way first: C1HEX@HEX OMi/Brennan 1.875 -&gt; Air-Way 1.75</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
@@ -1820,10 +1820,10 @@
         <v>2</v>
       </c>
       <c r="C23" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="D23" t="n">
-        <v>1.875</v>
+        <v>1.75</v>
       </c>
       <c r="E23" t="n">
         <v>1.5</v>
@@ -1857,12 +1857,12 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>Air-Way s55 only (double-pass 27 rows); D@BORE: OMi WebsitePartsInfo2026.xlsx Items!X106 Side 2 ID = 0.78 (table had 0.84) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; C1HEX@HEX: OMi WebsitePartsInfo2026.xlsx Items!R106 = 1.875 (table had 1.75) [user 2026-10-18 A19]</t>
+          <t>Air-Way s55 only (double-pass 27 rows); D@BORE: OMi WebsitePartsInfo2026.xlsx Items!X106 Side 2 ID = 0.78 (table had 0.84) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; C1HEX@HEX: OMi WebsitePartsInfo2026.xlsx Items!R106 = 1.875 (table had 1.75) [user 2026-10-18 A19]; W@HEX: Air-Way 2.38 (raw 07_RAW_EXTRACTS; OMi file / Brennan 2.4) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)]; C1HEX@HEX: Air-Way 1.75 (raw 07_RAW_EXTRACTS; OMi file / Brennan 1.875) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)]</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>A20 (user 2026-10-18): W@HEX 2.38 -&gt; OMi 2.40 (Items!L106; nut face at OMi's overall length) | A21 (user 2026-10-18): D@BORE 0.78 (OMi, batch 14) -&gt; Air-Way 0.84 (0.84 (07_RAW_EXTRACTS\1404.csv col 9 (D))) | A19 (user 2026-10-18, group 3 open): C1HEX@HEX 1.75 -&gt; OMi 1.875 (Items!R106, M051)</t>
+          <t>A20 (user 2026-10-18): W@HEX 2.38 -&gt; OMi 2.40 (Items!L106; nut face at OMi's overall length) | A21 (user 2026-10-18): D@BORE 0.78 (OMi, batch 14) -&gt; Air-Way 0.84 (0.84 (07_RAW_EXTRACTS\1404.csv col 9 (D))) | A19 (user 2026-10-18, group 3 open): C1HEX@HEX 1.75 -&gt; OMi 1.875 (Items!R106, M051) | 2026-10-20 Air-Way first: W@HEX OMi/Brennan 2.4 -&gt; Air-Way 2.38 | 2026-10-20 Air-Way first: C1HEX@HEX OMi/Brennan 1.875 -&gt; Air-Way 1.75</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
@@ -1886,10 +1886,10 @@
         <v>2.06</v>
       </c>
       <c r="C24" t="n">
-        <v>2.52</v>
+        <v>2.49</v>
       </c>
       <c r="D24" t="n">
-        <v>1.875</v>
+        <v>1.75</v>
       </c>
       <c r="E24" t="n">
         <v>1.88</v>
@@ -1923,12 +1923,12 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>Air-Way s55 only (double-pass 27 rows); C1HEX@HEX: OMi WebsitePartsInfo2026.xlsx Items!R107 = 1.875 (table had 1.75) [user 2026-10-18 A19]</t>
+          <t>Air-Way s55 only (double-pass 27 rows); C1HEX@HEX: OMi WebsitePartsInfo2026.xlsx Items!R107 = 1.875 (table had 1.75) [user 2026-10-18 A19]; W@HEX: Air-Way 2.49 (raw 07_RAW_EXTRACTS; OMi file / Brennan 2.52) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)]; C1HEX@HEX: Air-Way 1.75 (raw 07_RAW_EXTRACTS; OMi file / Brennan 1.875) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)]</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>A20 (user 2026-10-18): W@HEX 2.49 -&gt; OMi 2.52 (Items!L107; nut face at OMi's overall length) | A19 (user 2026-10-18, group 3 open): C1HEX@HEX 1.75 -&gt; OMi 1.875 (Items!R107, M051)</t>
+          <t>A20 (user 2026-10-18): W@HEX 2.49 -&gt; OMi 2.52 (Items!L107; nut face at OMi's overall length) | A19 (user 2026-10-18, group 3 open): C1HEX@HEX 1.75 -&gt; OMi 1.875 (Items!R107, M051) | 2026-10-20 Air-Way first: W@HEX OMi/Brennan 2.52 -&gt; Air-Way 2.49 | 2026-10-20 Air-Way first: C1HEX@HEX OMi/Brennan 1.875 -&gt; Air-Way 1.75</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
@@ -2021,7 +2021,7 @@
         <v>2.61</v>
       </c>
       <c r="D26" t="n">
-        <v>2.125</v>
+        <v>2</v>
       </c>
       <c r="E26" t="n">
         <v>1.88</v>
@@ -2055,12 +2055,12 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>Air-Way s55 only (double-pass 27 rows); C1HEX@HEX: OMi WebsitePartsInfo2026.xlsx Items!R109 = 2.125 (table had 2) [user 2026-10-18 A19]</t>
+          <t>Air-Way s55 only (double-pass 27 rows); C1HEX@HEX: OMi WebsitePartsInfo2026.xlsx Items!R109 = 2.125 (table had 2) [user 2026-10-18 A19]; C1HEX@HEX: Air-Way 2 (raw 07_RAW_EXTRACTS; OMi file / Brennan 2.125) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)]</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>A20 (user 2026-10-18): W@HEX 2.61 -&gt; OMi 2.54 (Items!L109; nut face at OMi's overall length) | A19 (user 2026-10-18, group 3 open): C1HEX@HEX 2 -&gt; OMi 2.125 (Items!R109, M051) | A20 HELD (2026-10-18): OMi overall length 2.54 as nut face breaks the measured NPSM swivel (W-L out of range; OMi gives no stem-tip length to pair) -&gt; kept at Air-Way W 2.61; user 2026-10-18: keep Air-Way W, reported to OMi (10_DRAWINGS/for_OMi_LATER)</t>
+          <t>A20 (user 2026-10-18): W@HEX 2.61 -&gt; OMi 2.54 (Items!L109; nut face at OMi's overall length) | A19 (user 2026-10-18, group 3 open): C1HEX@HEX 2 -&gt; OMi 2.125 (Items!R109, M051) | A20 HELD (2026-10-18): OMi overall length 2.54 as nut face breaks the measured NPSM swivel (W-L out of range; OMi gives no stem-tip length to pair) -&gt; kept at Air-Way W 2.61; user 2026-10-18: keep Air-Way W, reported to OMi (10_DRAWINGS/for_OMi_LATER) | 2026-10-20 Air-Way first: C1HEX@HEX OMi/Brennan 2.125 -&gt; Air-Way 2</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
@@ -2084,7 +2084,7 @@
         <v>2.13</v>
       </c>
       <c r="C27" t="n">
-        <v>2.69</v>
+        <v>2.55</v>
       </c>
       <c r="D27" t="n">
         <v>2.13</v>
@@ -2121,12 +2121,12 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>Air-Way s55 only (double-pass 27 rows); D@BORE: OMi WebsitePartsInfo2026.xlsx Items!X110 Side 2 ID = 1.25 (table had 1.26) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]</t>
+          <t>Air-Way s55 only (double-pass 27 rows); D@BORE: OMi WebsitePartsInfo2026.xlsx Items!X110 Side 2 ID = 1.25 (table had 1.26) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; W@HEX: Air-Way 2.55 (raw 07_RAW_EXTRACTS; OMi file / Brennan 2.69) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)]</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>A20 (user 2026-10-18): W@HEX 2.55 -&gt; OMi 2.69 (Items!L110; nut face at OMi's overall length) | A21 (user 2026-10-18): D@BORE 1.25 (OMi, batch 14) -&gt; Air-Way 1.26 (1.26 (07_RAW_EXTRACTS\1404.csv col 9 (D)))</t>
+          <t>A20 (user 2026-10-18): W@HEX 2.55 -&gt; OMi 2.69 (Items!L110; nut face at OMi's overall length) | A21 (user 2026-10-18): D@BORE 1.25 (OMi, batch 14) -&gt; Air-Way 1.26 (1.26 (07_RAW_EXTRACTS\1404.csv col 9 (D))) | 2026-10-20 Air-Way first: W@HEX OMi/Brennan 2.69 -&gt; Air-Way 2.55</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
